--- a/文档/Hediff/肾上腺素数值.xlsx
+++ b/文档/Hediff/肾上腺素数值.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RimMods\Rim-Hormones\RimHormones\文档\Hediff\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11655" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="244">
   <si>
     <t>肾上腺素系统数值总览 (Adrenaline)</t>
   </si>
@@ -341,9 +346,6 @@
     <t>AdrenalineBaseDecay</t>
   </si>
   <si>
-    <t>0.02</t>
-  </si>
-  <si>
     <t>每秒基础衰减量</t>
   </si>
   <si>
@@ -359,6 +361,18 @@
     <t>每点体鬄额外增加的每秒衰减</t>
   </si>
   <si>
+    <t>AdrenalineBloodingLowBase</t>
+  </si>
+  <si>
+    <t>每秒处于流血状态&lt;150%下生成量</t>
+  </si>
+  <si>
+    <t>AdrenalineBloodingHighBase</t>
+  </si>
+  <si>
+    <t>每秒处于流血状态下&gt;150%生成量</t>
+  </si>
+  <si>
     <t>关键公式</t>
   </si>
   <si>
@@ -651,6 +665,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">chance = (0.03 + 0.02 x (13 - </t>
     </r>
     <r>
@@ -800,7 +821,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,13 +869,6 @@
       <color rgb="FF808080"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1437,148 +1451,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2430,7 +2444,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2532,59 +2546,75 @@
       <c r="A8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" ht="33" spans="1:4">
+      <c r="A10" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="6">
+        <v>0.035</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
+      <c r="D10" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" ht="33" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0.065</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="11" t="s">
+      <c r="A12" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>113</v>
       </c>
       <c r="C13" s="8"/>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="11" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2660,11 +2690,22 @@
         <v>132</v>
       </c>
     </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
@@ -2672,6 +2713,7 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2691,12 +2733,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>41</v>
@@ -2708,7 +2750,7 @@
         <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5">
@@ -2730,16 +2772,16 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5">
       <c r="A4" s="18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>69</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>72</v>
@@ -2747,7 +2789,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5">
       <c r="A5" s="18" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>69</v>
@@ -2759,18 +2801,18 @@
         <v>71</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5">
       <c r="A6" s="18" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B6" s="14">
         <v>0.13</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D6" s="12">
         <v>0.4</v>
@@ -2781,24 +2823,24 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5">
       <c r="A7" s="18" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5">
       <c r="A8" s="18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B8" s="14">
         <v>-0.08</v>
@@ -2810,12 +2852,12 @@
         <v>-0.12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5">
       <c r="A9" s="18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>67</v>
@@ -2827,12 +2869,12 @@
         <v>-0.12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5">
       <c r="A10" s="18" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B10" s="14">
         <v>0.1</v>
@@ -2849,7 +2891,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5">
       <c r="A11" s="18" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B11" s="14">
         <v>0</v>
@@ -2866,7 +2908,7 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5">
       <c r="A12" s="18" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" s="14">
         <v>-0.012</v>
@@ -2878,12 +2920,12 @@
         <v>-0.03</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5">
       <c r="A13" s="18" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>39</v>
@@ -2895,12 +2937,12 @@
         <v>1.5</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -2938,12 +2980,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>86</v>
@@ -2952,91 +2994,91 @@
         <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3062,12 +3104,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>86</v>
@@ -3081,91 +3123,91 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -3173,7 +3215,7 @@
     </row>
     <row r="11" ht="15" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -3181,7 +3223,7 @@
     </row>
     <row r="12" ht="14.25" spans="1:4">
       <c r="A12" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3189,7 +3231,7 @@
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3197,63 +3239,63 @@
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:4">
       <c r="A16" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:4">
       <c r="A17" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4">
       <c r="A18" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -3264,60 +3306,60 @@
         <v>31</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4">
       <c r="A23" s="16" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:4">
       <c r="A24" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:4">
       <c r="A25" s="10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
